--- a/test_audit.xlsx
+++ b/test_audit.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Multilingual Audit" sheetId="1" r:id="rId1"/>
+    <sheet name="Audit" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,23 +397,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E11"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="45.83203125" customWidth="1"/>
+    <col min="3" max="3" width="40.83203125" customWidth="1"/>
+    <col min="4" max="4" width="25.83203125" customWidth="1"/>
+    <col min="5" max="5" width="45.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Lang ID</v>
+        <v>Language</v>
       </c>
       <c r="B1" t="str">
-        <v>Target Web URL</v>
+        <v>Page URL</v>
       </c>
       <c r="C1" t="str">
-        <v>Expected Page Content</v>
+        <v>Expected Content</v>
       </c>
       <c r="D1" t="str">
-        <v>Button Click CTA Label</v>
+        <v>Button Name</v>
       </c>
       <c r="E1" t="str">
-        <v>Expected Button Destination Redirect</v>
+        <v>Button Redirect URL</v>
       </c>
     </row>
     <row r="2">
@@ -467,9 +474,128 @@
         <v>http://localhost:3000/nl/about.html</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>de</v>
+      </c>
+      <c r="B5" t="str">
+        <v>http://localhost:3000/de/index.html</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Falsche Seite</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Mehr erfahren</v>
+      </c>
+      <c r="E5" t="str">
+        <v>http://localhost:3000/de/about.html</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>es</v>
+      </c>
+      <c r="B6" t="str">
+        <v>http://localhost:3000/es/index.html</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Bienvenido al sitio de prueba</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Saber más</v>
+      </c>
+      <c r="E6" t="str">
+        <v>http://localhost:3000/es/about.html</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>it</v>
+      </c>
+      <c r="B7" t="str">
+        <v>http://localhost:3000/it/index.html</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Benvenuto nel sito di test</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Scopri di più</v>
+      </c>
+      <c r="E7" t="str">
+        <v>http://localhost:3000/it/about.html</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>pt</v>
+      </c>
+      <c r="B8" t="str">
+        <v>http://localhost:3000/pt/index.html</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Bem-vindo ao site de teste</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Click Here</v>
+      </c>
+      <c r="E8" t="str">
+        <v>http://localhost:3000/pt/about.html</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>pl</v>
+      </c>
+      <c r="B9" t="str">
+        <v>http://localhost:3000/pl/index.html</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Witamy na stronie testowej</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Dowiedz się więcej</v>
+      </c>
+      <c r="E9" t="str">
+        <v>http://localhost:3000/pl/about.html</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>sv</v>
+      </c>
+      <c r="B10" t="str">
+        <v>http://localhost:3000/sv/index.html</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Välkommen till testsidan</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Läs mer</v>
+      </c>
+      <c r="E10" t="str">
+        <v>http://localhost:3000/sv/wrong.html</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>ja</v>
+      </c>
+      <c r="B11" t="str">
+        <v>http://localhost:3000/ja/index.html</v>
+      </c>
+      <c r="C11" t="str">
+        <v>テストサイトへようこそ</v>
+      </c>
+      <c r="D11" t="str">
+        <v>詳細を見る</v>
+      </c>
+      <c r="E11" t="str">
+        <v>http://localhost:3000/ja/about.html</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
   </ignoredErrors>
 </worksheet>
 </file>